--- a/outputs/full_factorial_design.xlsx
+++ b/outputs/full_factorial_design.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="3.71" hidden="0" customWidth="1"/>
